--- a/nodes_source_analyses/energy/energy/energy_production_methanol_synthesis_biogenic_waste_ccs.xlsx
+++ b/nodes_source_analyses/energy/energy/energy_production_methanol_synthesis_biogenic_waste_ccs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10412"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathijsbijkerk/Github/etdataset/nodes_source_analyses/energy/energy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robin/Desktop/Quintel/etdataset/nodes_source_analyses/energy/energy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E502F5E1-C1FC-F040-AD0F-9AA5D10894A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4238F102-CDC2-B240-9A63-51482DEE9026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14480" yWindow="-33340" windowWidth="30080" windowHeight="16180" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2020" yWindow="500" windowWidth="28800" windowHeight="15820" tabRatio="762" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <definedName name="Wp_to_kWp">#REF!</definedName>
     <definedName name="WP_to_MWp">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="223">
   <si>
     <t>Source</t>
   </si>
@@ -871,6 +871,12 @@
   </si>
   <si>
     <t>- captured</t>
+  </si>
+  <si>
+    <t>Is the actual CO2 capture rate</t>
+  </si>
+  <si>
+    <t>Taken from energy_hydrogen_biomass_gasification_ccs</t>
   </si>
 </sst>
 </file>
@@ -2593,7 +2599,7 @@
     <xf numFmtId="9" fontId="53" fillId="14" borderId="22" xfId="499" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="60" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="32" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2627,7 +2633,7 @@
     <xf numFmtId="0" fontId="48" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="60" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="501">
     <cellStyle name="Comma" xfId="496" builtinId="3"/>
@@ -3517,6 +3523,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover Sheet"/>
       <sheetName val="Changelog"/>
@@ -3630,6 +3639,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Title"/>
       <sheetName val="Description"/>
@@ -4691,13 +4703,13 @@
       </c>
       <c r="E33" s="75">
         <f>Notes!D97</f>
-        <v>0.52228799999999997</v>
+        <v>0.9</v>
       </c>
       <c r="F33" s="71"/>
       <c r="G33" s="71"/>
       <c r="H33" s="71"/>
       <c r="I33" s="102" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="J33" s="74"/>
     </row>
@@ -7422,7 +7434,7 @@
     </row>
     <row r="75" spans="1:25">
       <c r="C75" s="199"/>
-      <c r="F75" s="259" t="s">
+      <c r="F75" s="247" t="s">
         <v>219</v>
       </c>
       <c r="W75" s="164"/>
@@ -7430,7 +7442,7 @@
       <c r="Y75" s="163"/>
     </row>
     <row r="76" spans="1:25">
-      <c r="F76" s="259" t="s">
+      <c r="F76" s="247" t="s">
         <v>220</v>
       </c>
       <c r="W76" s="164"/>
@@ -7787,15 +7799,14 @@
       <c r="C97" s="245" t="s">
         <v>189</v>
       </c>
-      <c r="D97" s="247">
-        <f>ROUND(G86/D83,6)</f>
-        <v>0.52228799999999997</v>
+      <c r="D97" s="204">
+        <v>0.9</v>
       </c>
       <c r="E97" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="F97" s="245" t="s">
-        <v>214</v>
+      <c r="F97" s="259" t="s">
+        <v>221</v>
       </c>
       <c r="G97" s="245"/>
       <c r="H97" s="245"/>
